--- a/costos/calculadora-costos.xlsx
+++ b/costos/calculadora-costos.xlsx
@@ -5,22 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javi_\OneDrive\Escritorio\Carpeta Claude\pruebatecnica-promarketing\costos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javi_\OneDrive\Documentos\GitHub\promarketing-pruebatecnica\costos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC6E2697-DA73-4636-B8B1-8A17F2CE7752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA644DDD-E08D-4A8E-B6F5-E7273431C599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{26B685E1-6CF5-42DE-BF29-FD14178ECFAA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Detalle costos" sheetId="2" r:id="rId1"/>
-    <sheet name="Resumen" sheetId="1" r:id="rId2"/>
+    <sheet name="Detalle costos" sheetId="1" r:id="rId1"/>
+    <sheet name="Resumen" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -32,26 +29,110 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Estimacion</author>
+  </authors>
+  <commentList>
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Aptos Narrow"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Asuncion: 8 RPU x $0.42/RPU-h (ca-central-1) x ~40 h/mes de computo activo. Serverless solo factura el computo en uso; idle = $0.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
+    <t>Servicio</t>
+  </si>
+  <si>
     <t>Descripción</t>
   </si>
   <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Estimado mensual USD</t>
+  </si>
+  <si>
+    <t>EC2</t>
+  </si>
+  <si>
+    <t>Instancias privadas t3.micro + EBS (4, en 3 AZs)</t>
+  </si>
+  <si>
+    <t>RDS</t>
+  </si>
+  <si>
+    <t>PosgreSQL db.t3.micro, Multi-AZ, 20GB</t>
+  </si>
+  <si>
+    <t>ALB</t>
+  </si>
+  <si>
+    <t>Balanceador activo + LCU estimadas</t>
+  </si>
+  <si>
+    <t>NAT Gateway</t>
+  </si>
+  <si>
+    <t>NAT + EIP + datos procesados</t>
+  </si>
+  <si>
+    <t>S3 + CloudFront</t>
+  </si>
+  <si>
+    <t>Contenido estático privado + CDN</t>
+  </si>
+  <si>
+    <t>Redis</t>
+  </si>
+  <si>
+    <t>ElastiCache cache.t3.micro, 2 nodos Multi-AZ</t>
+  </si>
+  <si>
+    <t>VPC Endpoints</t>
+  </si>
+  <si>
+    <t>S3 Gateway + Secrets Manager Interface (3 AZs)</t>
+  </si>
+  <si>
+    <t>CloudWatch</t>
+  </si>
+  <si>
+    <t>Logs, almacenamiento, alarmas y SNS</t>
+  </si>
+  <si>
     <t>Redshift</t>
   </si>
   <si>
-    <t>ALB</t>
-  </si>
-  <si>
-    <t>NAT Gateway</t>
+    <t>Redshift Serverless 8 RPU (~40 h/mes activo)</t>
+  </si>
+  <si>
+    <t>Total mensual estimado</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Valor</t>
   </si>
   <si>
     <t>Costo mensual total</t>
@@ -67,69 +148,6 @@
   </si>
   <si>
     <t>Servicio de mayor costo</t>
-  </si>
-  <si>
-    <t>Servicio</t>
-  </si>
-  <si>
-    <t>Cantidad</t>
-  </si>
-  <si>
-    <t>EC2</t>
-  </si>
-  <si>
-    <t>Estimado mensual USD</t>
-  </si>
-  <si>
-    <t>Instancias privadas t3.micro + EBS</t>
-  </si>
-  <si>
-    <t>RDS</t>
-  </si>
-  <si>
-    <t>PosgreSQL db.t3.micro, Multi-AZ, 20GB</t>
-  </si>
-  <si>
-    <t>Balanceador activo + LCU estimadas</t>
-  </si>
-  <si>
-    <t>NAT + EIP + datos procesados</t>
-  </si>
-  <si>
-    <t>S3 + CloudFront</t>
-  </si>
-  <si>
-    <t>Contenido estático privado + CDN</t>
-  </si>
-  <si>
-    <t>Redis</t>
-  </si>
-  <si>
-    <t>ElastiCache cache.t3.micro, 1 nodo</t>
-  </si>
-  <si>
-    <t>VPC Endpoints</t>
-  </si>
-  <si>
-    <t>S3 Gateway + Secrets Manager Interface</t>
-  </si>
-  <si>
-    <t>CloudWatch</t>
-  </si>
-  <si>
-    <t>Logs, almacenamiento y alarmas</t>
-  </si>
-  <si>
-    <t>DW dc2.large, single-node</t>
-  </si>
-  <si>
-    <t>Total mensual estimado</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Valor</t>
   </si>
 </sst>
 </file>
@@ -190,7 +208,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -215,7 +233,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda [0]" xfId="1" builtinId="7"/>
@@ -223,13 +241,13 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+      <alignment horizontal="left" vertical="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -245,24 +263,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{78D33F86-8447-4945-92E2-4387645A6ED5}" name="Tabla1" displayName="Tabla1" ref="A1:D13" totalsRowShown="0">
-  <autoFilter ref="A1:D13" xr:uid="{78D33F86-8447-4945-92E2-4387645A6ED5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="A1:D13" totalsRowShown="0">
+  <autoFilter ref="A1:D13" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{506C6553-EAB7-4D70-A1AD-D967AF070D4B}" name="Servicio"/>
-    <tableColumn id="2" xr3:uid="{5ADB6187-92F2-46EB-931E-51D0647D51F5}" name="Descripción"/>
-    <tableColumn id="3" xr3:uid="{FF79E979-CB6D-4CAC-B7FC-5EE5219EF8A9}" name="Cantidad"/>
-    <tableColumn id="6" xr3:uid="{F6E021F8-5A80-4DBF-9758-C5B1B231E28C}" name="Estimado mensual USD" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Servicio"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Descripción"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Cantidad"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Estimado mensual USD" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{697A40C8-34ED-435C-A7D3-7BCB628026C6}" name="Tabla2" displayName="Tabla2" ref="A1:B6" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:B6" xr:uid="{697A40C8-34ED-435C-A7D3-7BCB628026C6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabla2" displayName="Tabla2" ref="A1:B6" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:B6" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{D0141F3A-DAB9-4FC9-8F1B-67113496B265}" name="Item" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{995A25EB-B1FC-49E3-894C-B861AF4E1971}" name="Valor"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Item" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Valor"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -584,7 +602,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE94B8BF-80B6-4C69-9D85-7521F556D1A8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -601,124 +619,125 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>4</v>
       </c>
       <c r="D2" s="6">
-        <f>33.87+31.18</f>
-        <v>65.05</v>
+        <f>33.87</f>
+        <v>33.869999999999997</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>75.89</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4" s="6">
-        <v>58.54</v>
+        <v>50.19</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5" s="6">
-        <v>134.5</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" s="6">
-        <f>3.6+200</f>
-        <v>203.6</v>
+        <f>1.49+200</f>
+        <v>201.49</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" s="6">
-        <v>13.87</v>
+        <v>27.74</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>2</v>
       </c>
       <c r="D8" s="6">
-        <v>13.87</v>
+        <f>7+1.49+0.4</f>
+        <v>8.89</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -729,16 +748,16 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" s="6">
-        <v>200.75</v>
+        <v>100.65</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -746,25 +765,26 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="10">
-        <f>SUM(D2:D11)</f>
-        <v>822.37</v>
+        <f>SUM(D2:D10)</f>
+        <v>798.2399999999999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA752339-C621-4224-8EFA-E02AB3DDCC4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -776,60 +796,60 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B2" s="6">
         <f>'Detalle costos'!D13</f>
-        <v>822.37</v>
+        <v>798.2399999999999</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B3" s="6">
         <f>B2*12</f>
-        <v>9868.44</v>
+        <v>9578.8799999999992</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="B4" s="6">
-        <f>SUM('Detalle costos'!D2,'Detalle costos'!D3,'Detalle costos'!D7,'Detalle costos'!D10)</f>
-        <v>355.56</v>
+        <f>SUM('Detalle costos'!D2,'Detalle costos'!D3,'Detalle costos'!D7)</f>
+        <v>157.72</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7">
-        <f>SUM('Detalle costos'!D4,'Detalle costos'!D5,'Detalle costos'!D6,'Detalle costos'!D8,'Detalle costos'!D9)</f>
-        <v>466.81</v>
+        <f>SUM('Detalle costos'!D4,'Detalle costos'!D5,'Detalle costos'!D6,'Detalle costos'!D8,'Detalle costos'!D9,'Detalle costos'!D10)</f>
+        <v>640.52</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="B6" s="8" t="str">
         <f>_xlfn.XLOOKUP(MAX('Detalle costos'!D2:D10),'Detalle costos'!D2:D10,'Detalle costos'!A2:A10)&amp;" - "&amp;TEXT(MAX('Detalle costos'!D2:D10),"$###,##")</f>
-        <v>S3 + CloudFront - $203,6</v>
+        <v>NAT Gateway - $223,</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="2"/>
@@ -884,218 +904,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B07DE3DA4DB4154B8D7E8E250B306283" ma:contentTypeVersion="5" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="f67a9ced3fc6aae2bfd297ad2e29aa40">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2f1c098d-6a8f-47a4-bd24-10a5618511b4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c6e553390d317e826896ea65259aa84d" ns3:_="">
-    <xsd:import namespace="2f1c098d-6a8f-47a4-bd24-10a5618511b4"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:_activity" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2f1c098d-6a8f-47a4-bd24-10a5618511b4" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_activity" ma:index="10" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="12" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="2f1c098d-6a8f-47a4-bd24-10a5618511b4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{04736FFF-81DB-499D-83BC-A60308C90945}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3A651CE-4A1A-427F-A00D-A3BB69358571}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="2f1c098d-6a8f-47a4-bd24-10a5618511b4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2EEA1B3-79C0-4BAE-94D2-1B8B82D6124B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="2f1c098d-6a8f-47a4-bd24-10a5618511b4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>